--- a/artfynd/A 22629-2020 artfynd.xlsx
+++ b/artfynd/A 22629-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22629-2020 artfynd.xlsx
+++ b/artfynd/A 22629-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,215 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123934586</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100682</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Luresten, Luresten, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566676</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6310439</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123934540</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5361</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Luresten, Luresten, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566750</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6310428</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22629-2020 artfynd.xlsx
+++ b/artfynd/A 22629-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>123934586</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2020 artfynd.xlsx
+++ b/artfynd/A 22629-2020 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123934586</v>
+        <v>123934540</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>5361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566676</v>
+        <v>566750</v>
       </c>
       <c r="R3" t="n">
-        <v>6310439</v>
+        <v>6310428</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123934540</v>
+        <v>123934586</v>
       </c>
       <c r="B4" t="n">
-        <v>5361</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566750</v>
+        <v>566676</v>
       </c>
       <c r="R4" t="n">
-        <v>6310428</v>
+        <v>6310439</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,11 +984,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 22629-2020 artfynd.xlsx
+++ b/artfynd/A 22629-2020 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123934540</v>
+        <v>123934586</v>
       </c>
       <c r="B3" t="n">
-        <v>5361</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566750</v>
+        <v>566676</v>
       </c>
       <c r="R3" t="n">
-        <v>6310428</v>
+        <v>6310439</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123934586</v>
+        <v>123934540</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>5361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566676</v>
+        <v>566750</v>
       </c>
       <c r="R4" t="n">
-        <v>6310439</v>
+        <v>6310428</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,6 +979,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 22629-2020 artfynd.xlsx
+++ b/artfynd/A 22629-2020 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123934586</v>
+        <v>123934540</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>5361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>101728</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566676</v>
+        <v>566750</v>
       </c>
       <c r="R3" t="n">
-        <v>6310439</v>
+        <v>6310428</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123934540</v>
+        <v>123934586</v>
       </c>
       <c r="B4" t="n">
-        <v>5361</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566750</v>
+        <v>566676</v>
       </c>
       <c r="R4" t="n">
-        <v>6310428</v>
+        <v>6310439</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,11 +984,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
